--- a/src/test/resources/teda/MULTIPLE_TABLES_IN_ONE_SHEET.xlsx
+++ b/src/test/resources/teda/MULTIPLE_TABLES_IN_ONE_SHEET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrick/Projects/teda-framework/src/test/resources/teda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97A577D-FD9F-E24A-9E8B-A32A3CC034B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6083DA72-B998-8D48-B15D-CDD8F5C473D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="20340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cockpit" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="24">
   <si>
     <t>#Teda</t>
   </si>
@@ -104,7 +104,7 @@
     <numFmt numFmtId="164" formatCode="0.000000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +116,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -156,7 +162,16 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -192,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:F5" totalsRowShown="0">
-  <autoFilter ref="C4:F5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:F6" totalsRowShown="0">
+  <autoFilter ref="C4:F6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TRUNCATE"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="LOAD"/>
@@ -208,8 +223,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13578" displayName="Table13578" ref="C4:F8" totalsRowShown="0">
   <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NAME" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NAME" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AGE"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="AVERAGE"/>
   </tableColumns>
@@ -221,8 +236,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}" name="Table135783" displayName="Table135783" ref="C11:F15" totalsRowShown="0">
   <autoFilter ref="C11:F15" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E3B5017E-96D8-6A48-BAB0-36B8D8FC37E8}" name="#ID" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{834A28C9-8705-AD44-AAA8-C205E2253100}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{E3B5017E-96D8-6A48-BAB0-36B8D8FC37E8}" name="#ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{834A28C9-8705-AD44-AAA8-C205E2253100}" name="NAME" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{1AE306CE-BE15-8546-B06A-E86CE63B2DA2}" name="AGE"/>
     <tableColumn id="4" xr3:uid="{5B577E32-7D9F-9D42-8EA6-E4783B916456}" name="AVERAGE"/>
   </tableColumns>
@@ -234,10 +249,23 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table4" displayName="Table4" ref="C4:F8">
   <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="NAME" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="NAME" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="AGE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AVERAGE" totalsRowFunction="sum" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AVERAGE" totalsRowFunction="sum" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}" name="Table44" displayName="Table44" ref="C11:F15">
+  <autoFilter ref="C11:F15" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2ADFE462-C6A8-4242-85D8-992F4DF6A472}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{8C38C0F2-429F-CC4A-B256-6CEBE3322318}" name="NAME" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{AB14713F-A401-D849-AEA9-960202F43827}" name="AGE"/>
+    <tableColumn id="4" xr3:uid="{E6D947CC-9E32-0E4F-BF7B-904CBFA7D13F}" name="AVERAGE" totalsRowFunction="sum" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -566,13 +594,18 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -586,6 +619,7 @@
       <c r="E10" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -807,7 +841,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B3:F9"/>
+  <dimension ref="B3:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
@@ -900,11 +934,90 @@
       <c r="D9" s="2"/>
       <c r="F9" s="2"/>
     </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+      <c r="F13" s="4">
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <v>21</v>
+      </c>
+      <c r="F14" s="4">
+        <v>24.33</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>66</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4.3939494940000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>